--- a/external_docs/exports/qbo/profit_and_loss_last_12_months.xlsx
+++ b/external_docs/exports/qbo/profit_and_loss_last_12_months.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Profit and Loss — 2025-07-13 to 2026-07-13</t>
+          <t>Profit and Loss — 2025-07-14 to 2026-07-14</t>
         </is>
       </c>
     </row>
@@ -449,7 +449,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>557481.4</v>
+        <v>562402.24</v>
       </c>
     </row>
     <row r="5">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>90493.66</v>
+        <v>94940.25</v>
       </c>
     </row>
     <row r="9">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>365991.07</v>
+        <v>366449.07</v>
       </c>
     </row>
     <row r="14">
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2247.06</v>
+        <v>2263.31</v>
       </c>
     </row>
     <row r="17">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>183019.14</v>
+        <v>182919.16</v>
       </c>
     </row>
     <row r="20">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>71222.42999999999</v>
+        <v>71122.45</v>
       </c>
     </row>
     <row r="23">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>374462.26</v>
+        <v>379483.08</v>
       </c>
     </row>
     <row r="24">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>351497.67</v>
+        <v>351822.23</v>
       </c>
     </row>
     <row r="26">
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>13795.6</v>
+        <v>14120.16</v>
       </c>
     </row>
     <row r="54">
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>22964.59</v>
+        <v>27660.85</v>
       </c>
     </row>
     <row r="84">
@@ -1335,7 +1335,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>28276.12</v>
+        <v>32972.38</v>
       </c>
     </row>
   </sheetData>
